--- a/Sindhi Muslim/PTM/PTM.xlsx
+++ b/Sindhi Muslim/PTM/PTM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\PTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4561E7F3-A82A-40A0-9E87-0F14C6898C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E566DA94-B066-4DEA-A261-5BFF96CAFC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{36001918-ECFB-49B7-8B7C-4207408CF352}"/>
   </bookViews>
@@ -134,11 +134,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,14 +466,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -491,14 +491,14 @@
       <c r="U1" s="1"/>
     </row>
     <row r="2" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -516,14 +516,14 @@
       <c r="U2" s="1"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -541,14 +541,14 @@
       <c r="U3" s="1"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -566,22 +566,22 @@
       <c r="U4" s="1"/>
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Sindhi Muslim/PTM/PTM.xlsx
+++ b/Sindhi Muslim/PTM/PTM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\PTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E566DA94-B066-4DEA-A261-5BFF96CAFC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8580A8B-88D9-4EAC-9D0D-B74A2E5EB4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{36001918-ECFB-49B7-8B7C-4207408CF352}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{36001918-ECFB-49B7-8B7C-4207408CF352}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,16 +54,16 @@
     <t>MALIR KARACHI SEMIS CODE# 408170153</t>
   </si>
   <si>
-    <t>Month - November 2024</t>
-  </si>
-  <si>
-    <t>Parents Teacher Meeting</t>
-  </si>
-  <si>
     <t>GR No</t>
   </si>
   <si>
     <t>Student Name</t>
+  </si>
+  <si>
+    <t>Parents Teacher Meeting - Month - May-2025</t>
+  </si>
+  <si>
+    <t>Teacher Name:_______________________                                           Class:_______________________</t>
   </si>
 </sst>
 </file>
@@ -517,7 +517,7 @@
     </row>
     <row r="3" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -540,9 +540,9 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
     </row>
-    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -570,10 +570,10 @@
         <v>0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>1</v>

--- a/Sindhi Muslim/PTM/PTM.xlsx
+++ b/Sindhi Muslim/PTM/PTM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\PTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8580A8B-88D9-4EAC-9D0D-B74A2E5EB4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CCEFB7-5776-4AF5-B73D-3F89BE18D81F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{36001918-ECFB-49B7-8B7C-4207408CF352}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{36001918-ECFB-49B7-8B7C-4207408CF352}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,10 +60,10 @@
     <t>Student Name</t>
   </si>
   <si>
-    <t>Parents Teacher Meeting - Month - May-2025</t>
-  </si>
-  <si>
     <t>Teacher Name:_______________________                                           Class:_______________________</t>
+  </si>
+  <si>
+    <t>Parents Teacher Meeting - Month - August-2025</t>
   </si>
 </sst>
 </file>
@@ -517,7 +517,7 @@
     </row>
     <row r="3" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -542,7 +542,7 @@
     </row>
     <row r="4" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
